--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/2.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/2.xlsx
@@ -426,13 +426,13 @@
         <v>-3.845403119859709</v>
       </c>
       <c r="E2">
-        <v>-14.32809836545062</v>
+        <v>-9.444791248435244</v>
       </c>
       <c r="F2">
-        <v>-0.4702535530405507</v>
+        <v>-0.9389487997489278</v>
       </c>
       <c r="G2">
-        <v>-10.98881317721883</v>
+        <v>-5.633793967773864</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.716468415470234</v>
       </c>
       <c r="E3">
-        <v>-14.84637315868048</v>
+        <v>-8.103036099280571</v>
       </c>
       <c r="F3">
-        <v>-0.308771611538815</v>
+        <v>-0.4640581932350132</v>
       </c>
       <c r="G3">
-        <v>-10.95465894200657</v>
+        <v>-5.313317058062898</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.580614823828776</v>
       </c>
       <c r="E4">
-        <v>-15.32056778591967</v>
+        <v>-10.41128987047031</v>
       </c>
       <c r="F4">
-        <v>-0.2601464449944841</v>
+        <v>-0.4303701476979629</v>
       </c>
       <c r="G4">
-        <v>-9.950270460217421</v>
+        <v>-4.444741617840728</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.453952580431267</v>
       </c>
       <c r="E5">
-        <v>-16.12348434137566</v>
+        <v>-10.8164116836705</v>
       </c>
       <c r="F5">
-        <v>-0.4634079248238156</v>
+        <v>-0.5526396614533783</v>
       </c>
       <c r="G5">
-        <v>-10.14084708961153</v>
+        <v>-4.308843264513206</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.34332375371839</v>
       </c>
       <c r="E6">
-        <v>-16.74007230531204</v>
+        <v>-11.81308352801867</v>
       </c>
       <c r="F6">
-        <v>0.09467147811623934</v>
+        <v>-0.6883063612142701</v>
       </c>
       <c r="G6">
-        <v>-9.590619046308246</v>
+        <v>-5.598625835099735</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.260979604735492</v>
       </c>
       <c r="E7">
-        <v>-17.45582479306838</v>
+        <v>-11.29517101270943</v>
       </c>
       <c r="F7">
-        <v>-0.4376978857431273</v>
+        <v>-0.271397331059307</v>
       </c>
       <c r="G7">
-        <v>-9.15970606257105</v>
+        <v>-3.975277562001616</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.212139901705668</v>
       </c>
       <c r="E8">
-        <v>-16.44453503462345</v>
+        <v>-11.99122463853241</v>
       </c>
       <c r="F8">
-        <v>-0.2683025504424481</v>
+        <v>-0.7736886745230236</v>
       </c>
       <c r="G8">
-        <v>-9.200196336614598</v>
+        <v>-3.856310311920829</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.201412366597662</v>
       </c>
       <c r="E9">
-        <v>-18.41177659913958</v>
+        <v>-12.27624226410117</v>
       </c>
       <c r="F9">
-        <v>-0.4739315043089805</v>
+        <v>0.1477019025086581</v>
       </c>
       <c r="G9">
-        <v>-9.220707252582686</v>
+        <v>-3.663446671099787</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.223676877737283</v>
       </c>
       <c r="E10">
-        <v>-19.10776682632645</v>
+        <v>-13.63621546418871</v>
       </c>
       <c r="F10">
-        <v>0.08653691022074821</v>
+        <v>-0.2517467995300971</v>
       </c>
       <c r="G10">
-        <v>-9.301920767400503</v>
+        <v>-3.03269745072773</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.272489801860866</v>
       </c>
       <c r="E11">
-        <v>-18.90712825694261</v>
+        <v>-13.44664901375362</v>
       </c>
       <c r="F11">
-        <v>-0.1986940092178028</v>
+        <v>-0.2152191105362501</v>
       </c>
       <c r="G11">
-        <v>-9.009924860825517</v>
+        <v>-4.171642266226585</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.335248534976234</v>
       </c>
       <c r="E12">
-        <v>-20.27350019080298</v>
+        <v>-15.80089849543926</v>
       </c>
       <c r="F12">
-        <v>0.217617768039742</v>
+        <v>0.8464231798308187</v>
       </c>
       <c r="G12">
-        <v>-8.498700698199352</v>
+        <v>-3.190724362252146</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.397318630889557</v>
       </c>
       <c r="E13">
-        <v>-20.1128072906408</v>
+        <v>-15.8440186249403</v>
       </c>
       <c r="F13">
-        <v>0.4310631967190906</v>
+        <v>0.3898519184298152</v>
       </c>
       <c r="G13">
-        <v>-8.334393528610159</v>
+        <v>-4.460307732918734</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.446347947991621</v>
       </c>
       <c r="E14">
-        <v>-21.22543524042937</v>
+        <v>-15.02918312589612</v>
       </c>
       <c r="F14">
-        <v>0.3008140197725075</v>
+        <v>0.53861593519637</v>
       </c>
       <c r="G14">
-        <v>-7.859741861485564</v>
+        <v>-2.447317680858114</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.469875357730216</v>
       </c>
       <c r="E15">
-        <v>-22.03308857969738</v>
+        <v>-15.8861153193156</v>
       </c>
       <c r="F15">
-        <v>0.9027355958731291</v>
+        <v>0.9791839667426898</v>
       </c>
       <c r="G15">
-        <v>-8.176835831768742</v>
+        <v>-2.775249525952137</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.46269578713311</v>
       </c>
       <c r="E16">
-        <v>-22.27037156075129</v>
+        <v>-17.34753992259697</v>
       </c>
       <c r="F16">
-        <v>1.09753116084585</v>
+        <v>1.007207635979397</v>
       </c>
       <c r="G16">
-        <v>-8.037462664809768</v>
+        <v>-3.234745230693657</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.421258882208516</v>
       </c>
       <c r="E17">
-        <v>-22.8073897078989</v>
+        <v>-17.76687208723324</v>
       </c>
       <c r="F17">
-        <v>1.308930522040283</v>
+        <v>1.895230745658912</v>
       </c>
       <c r="G17">
-        <v>-7.345036322784829</v>
+        <v>-2.283502694502836</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.347950440397308</v>
       </c>
       <c r="E18">
-        <v>-24.655953554096</v>
+        <v>-18.61012376067554</v>
       </c>
       <c r="F18">
-        <v>1.697668433560841</v>
+        <v>1.793603319213857</v>
       </c>
       <c r="G18">
-        <v>-7.153068455449515</v>
+        <v>-1.838808580215972</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.246921193858285</v>
       </c>
       <c r="E19">
-        <v>-24.59776719157145</v>
+        <v>-18.66131363085825</v>
       </c>
       <c r="F19">
-        <v>1.684833709021865</v>
+        <v>1.953474914484551</v>
       </c>
       <c r="G19">
-        <v>-7.282007337849454</v>
+        <v>-2.29411744624764</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.123689347525759</v>
       </c>
       <c r="E20">
-        <v>-25.69052419741437</v>
+        <v>-20.36180543395255</v>
       </c>
       <c r="F20">
-        <v>2.036775540510069</v>
+        <v>2.10967021522162</v>
       </c>
       <c r="G20">
-        <v>-6.273251550164687</v>
+        <v>-1.98542996559976</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.987705533849439</v>
       </c>
       <c r="E21">
-        <v>-25.48425673483899</v>
+        <v>-21.37206722879774</v>
       </c>
       <c r="F21">
-        <v>2.387647121313856</v>
+        <v>2.675108834168145</v>
       </c>
       <c r="G21">
-        <v>-6.985046943055029</v>
+        <v>-1.780156744840898</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.845887951787352</v>
       </c>
       <c r="E22">
-        <v>-26.40333317706573</v>
+        <v>-21.71433382277147</v>
       </c>
       <c r="F22">
-        <v>2.767269677934007</v>
+        <v>3.054762868749604</v>
       </c>
       <c r="G22">
-        <v>-7.079188470817058</v>
+        <v>-1.318370747450887</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.707129914047012</v>
       </c>
       <c r="E23">
-        <v>-27.13117669042255</v>
+        <v>-23.10150050927506</v>
       </c>
       <c r="F23">
-        <v>3.036803863456911</v>
+        <v>3.115581603463144</v>
       </c>
       <c r="G23">
-        <v>-6.051670658255386</v>
+        <v>-1.71485387336483</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.57569440910996</v>
       </c>
       <c r="E24">
-        <v>-27.53057451247706</v>
+        <v>-22.91453340292038</v>
       </c>
       <c r="F24">
-        <v>3.225380045969413</v>
+        <v>3.521582691658043</v>
       </c>
       <c r="G24">
-        <v>-6.615617488898708</v>
+        <v>-1.32609146178026</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.453086152567176</v>
       </c>
       <c r="E25">
-        <v>-27.27717016395584</v>
+        <v>-23.80510310126883</v>
       </c>
       <c r="F25">
-        <v>3.050660793370941</v>
+        <v>3.558340666789868</v>
       </c>
       <c r="G25">
-        <v>-6.208519611239962</v>
+        <v>-1.082897163458896</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.338176135614445</v>
       </c>
       <c r="E26">
-        <v>-27.34711697347831</v>
+        <v>-22.65707154168829</v>
       </c>
       <c r="F26">
-        <v>2.991079639557184</v>
+        <v>3.418210723462693</v>
       </c>
       <c r="G26">
-        <v>-6.550058682141003</v>
+        <v>-1.575805547340241</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.222459579532704</v>
       </c>
       <c r="E27">
-        <v>-27.77698689713043</v>
+        <v>-22.65378839803273</v>
       </c>
       <c r="F27">
-        <v>2.936798380386537</v>
+        <v>3.837369599483659</v>
       </c>
       <c r="G27">
-        <v>-7.117132516930477</v>
+        <v>-1.399098641477905</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.099846805222972</v>
       </c>
       <c r="E28">
-        <v>-27.4020700055614</v>
+        <v>-23.03925210556563</v>
       </c>
       <c r="F28">
-        <v>2.958369067555437</v>
+        <v>3.343935988658078</v>
       </c>
       <c r="G28">
-        <v>-6.896391617740393</v>
+        <v>-1.978155497402471</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.95848623740708</v>
       </c>
       <c r="E29">
-        <v>-28.15194907343955</v>
+        <v>-22.47924289588108</v>
       </c>
       <c r="F29">
-        <v>2.719426490217919</v>
+        <v>3.728381300297328</v>
       </c>
       <c r="G29">
-        <v>-6.725905907954765</v>
+        <v>-2.856400697560324</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.79082900518277</v>
       </c>
       <c r="E30">
-        <v>-27.23952948800408</v>
+        <v>-22.82464319386812</v>
       </c>
       <c r="F30">
-        <v>2.952618541045203</v>
+        <v>3.450137659901391</v>
       </c>
       <c r="G30">
-        <v>-7.54658535707372</v>
+        <v>-2.044406641909219</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.591721175712911</v>
       </c>
       <c r="E31">
-        <v>-27.64657590265754</v>
+        <v>-22.31214673347205</v>
       </c>
       <c r="F31">
-        <v>2.65827640854326</v>
+        <v>3.594845161496437</v>
       </c>
       <c r="G31">
-        <v>-7.244781879257554</v>
+        <v>-2.686964978673718</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.359373234634961</v>
       </c>
       <c r="E32">
-        <v>-27.47083035489386</v>
+        <v>-21.73007932689614</v>
       </c>
       <c r="F32">
-        <v>2.526544453945665</v>
+        <v>2.827934336310626</v>
       </c>
       <c r="G32">
-        <v>-8.089407683317338</v>
+        <v>-2.047139899468236</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.100084230668171</v>
       </c>
       <c r="E33">
-        <v>-27.5045040876149</v>
+        <v>-22.21213538501265</v>
       </c>
       <c r="F33">
-        <v>2.475235377016264</v>
+        <v>2.677849073536606</v>
       </c>
       <c r="G33">
-        <v>-7.140957466673605</v>
+        <v>-2.297582416214414</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.8194717468370176</v>
       </c>
       <c r="E34">
-        <v>-26.35558041865485</v>
+        <v>-21.55033513658369</v>
       </c>
       <c r="F34">
-        <v>2.377608965126731</v>
+        <v>3.101958273156703</v>
       </c>
       <c r="G34">
-        <v>-7.981055184981354</v>
+        <v>-2.618390729302883</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.5314063155600494</v>
       </c>
       <c r="E35">
-        <v>-26.42086289994942</v>
+        <v>-22.68883425837809</v>
       </c>
       <c r="F35">
-        <v>2.251823031746432</v>
+        <v>2.522157420180439</v>
       </c>
       <c r="G35">
-        <v>-7.446688566696426</v>
+        <v>-2.421258219233004</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.2475986721041763</v>
       </c>
       <c r="E36">
-        <v>-26.18501997362995</v>
+        <v>-20.42972348711959</v>
       </c>
       <c r="F36">
-        <v>2.328485121405915</v>
+        <v>2.605260894764091</v>
       </c>
       <c r="G36">
-        <v>-6.806036619657964</v>
+        <v>-2.052783600550481</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.01758056238834588</v>
       </c>
       <c r="E37">
-        <v>-26.51878209341728</v>
+        <v>-20.31969515415522</v>
       </c>
       <c r="F37">
-        <v>1.990849194964059</v>
+        <v>2.953975406850988</v>
       </c>
       <c r="G37">
-        <v>-6.881425966207765</v>
+        <v>-2.422488677317796</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.2511714943402168</v>
       </c>
       <c r="E38">
-        <v>-25.79106990580667</v>
+        <v>-21.02284489874823</v>
       </c>
       <c r="F38">
-        <v>2.228443190169819</v>
+        <v>2.418157549493767</v>
       </c>
       <c r="G38">
-        <v>-7.148067873792922</v>
+        <v>-2.186125882283195</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.4440538278251469</v>
       </c>
       <c r="E39">
-        <v>-25.25124863324832</v>
+        <v>-18.63285217172004</v>
       </c>
       <c r="F39">
-        <v>2.266594479273153</v>
+        <v>2.060108993512126</v>
       </c>
       <c r="G39">
-        <v>-6.641145392631189</v>
+        <v>-2.185364638881405</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.5880760445790797</v>
       </c>
       <c r="E40">
-        <v>-25.05701785458533</v>
+        <v>-20.34510895028627</v>
       </c>
       <c r="F40">
-        <v>1.729936657369493</v>
+        <v>2.183194449159299</v>
       </c>
       <c r="G40">
-        <v>-6.283390524783371</v>
+        <v>-1.401986116450216</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.6815461412161482</v>
       </c>
       <c r="E41">
-        <v>-25.54616097452384</v>
+        <v>-18.04885110674286</v>
       </c>
       <c r="F41">
-        <v>1.838441189992589</v>
+        <v>2.53662402850293</v>
       </c>
       <c r="G41">
-        <v>-5.881411352757359</v>
+        <v>-1.765873587392635</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.7240828855699502</v>
       </c>
       <c r="E42">
-        <v>-24.56082842909088</v>
+        <v>-19.33139645824724</v>
       </c>
       <c r="F42">
-        <v>1.840036625610381</v>
+        <v>2.272171048628799</v>
       </c>
       <c r="G42">
-        <v>-6.021270140507131</v>
+        <v>-1.766086866793999</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.7201460210088846</v>
       </c>
       <c r="E43">
-        <v>-24.06208947273011</v>
+        <v>-16.80828470928958</v>
       </c>
       <c r="F43">
-        <v>1.504797994432227</v>
+        <v>2.021589909281948</v>
       </c>
       <c r="G43">
-        <v>-5.535714974140501</v>
+        <v>-1.460401703873011</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.6749658771502998</v>
       </c>
       <c r="E44">
-        <v>-24.2352402048874</v>
+        <v>-18.58509941330916</v>
       </c>
       <c r="F44">
-        <v>1.550339977503338</v>
+        <v>2.099075396139814</v>
       </c>
       <c r="G44">
-        <v>-5.57797710782615</v>
+        <v>-0.2408143061076826</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.5951730961438667</v>
       </c>
       <c r="E45">
-        <v>-23.51738650519149</v>
+        <v>-18.11578648105023</v>
       </c>
       <c r="F45">
-        <v>1.367983177451055</v>
+        <v>2.000236254372583</v>
       </c>
       <c r="G45">
-        <v>-6.031300834814353</v>
+        <v>-0.06582676034249589</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.4857678955660238</v>
       </c>
       <c r="E46">
-        <v>-23.42438523449597</v>
+        <v>-17.65399534411804</v>
       </c>
       <c r="F46">
-        <v>1.3923785974635</v>
+        <v>2.185160993373545</v>
       </c>
       <c r="G46">
-        <v>-5.412071983337506</v>
+        <v>-0.3001617604533591</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.3521626560788824</v>
       </c>
       <c r="E47">
-        <v>-23.14954309002244</v>
+        <v>-17.64141977179874</v>
       </c>
       <c r="F47">
-        <v>1.02180512635153</v>
+        <v>1.912580072543145</v>
       </c>
       <c r="G47">
-        <v>-5.507394750860934</v>
+        <v>-0.9551460832634755</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.19698978928866</v>
       </c>
       <c r="E48">
-        <v>-22.81708517074932</v>
+        <v>-16.5011771875114</v>
       </c>
       <c r="F48">
-        <v>0.9822191049065473</v>
+        <v>1.723158955279787</v>
       </c>
       <c r="G48">
-        <v>-5.443112339289852</v>
+        <v>-0.4892815274750743</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.02369469614917329</v>
       </c>
       <c r="E49">
-        <v>-22.92755729416644</v>
+        <v>-15.59985689186873</v>
       </c>
       <c r="F49">
-        <v>1.044210807862451</v>
+        <v>1.554746892086231</v>
       </c>
       <c r="G49">
-        <v>-4.990697510673615</v>
+        <v>-1.302112294623838</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.1656405724521567</v>
       </c>
       <c r="E50">
-        <v>-21.47549757513293</v>
+        <v>-17.53424437745921</v>
       </c>
       <c r="F50">
-        <v>0.7820954807990202</v>
+        <v>1.838437876522978</v>
       </c>
       <c r="G50">
-        <v>-5.570089051197244</v>
+        <v>-0.6911094655965186</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.3698148964788362</v>
       </c>
       <c r="E51">
-        <v>-21.68446853669089</v>
+        <v>-15.58756661341192</v>
       </c>
       <c r="F51">
-        <v>0.9933722436178398</v>
+        <v>1.705849390030889</v>
       </c>
       <c r="G51">
-        <v>-5.49288518912507</v>
+        <v>-1.198468349225658</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.5848436043082638</v>
       </c>
       <c r="E52">
-        <v>-21.21038259282788</v>
+        <v>-16.11886076941382</v>
       </c>
       <c r="F52">
-        <v>0.8471670537585326</v>
+        <v>1.622151147652027</v>
       </c>
       <c r="G52">
-        <v>-5.44620324999885</v>
+        <v>-0.7778518387419993</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.8101279933371014</v>
       </c>
       <c r="E53">
-        <v>-20.73102097674593</v>
+        <v>-15.14316481666918</v>
       </c>
       <c r="F53">
-        <v>0.7398321759081895</v>
+        <v>1.528563855218544</v>
       </c>
       <c r="G53">
-        <v>-5.421469401883756</v>
+        <v>-0.1848891658485068</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.039644027096861</v>
       </c>
       <c r="E54">
-        <v>-20.54161755137512</v>
+        <v>-14.39989279236823</v>
       </c>
       <c r="F54">
-        <v>0.5027434848181374</v>
+        <v>1.028352542303257</v>
       </c>
       <c r="G54">
-        <v>-5.363129282556828</v>
+        <v>-0.4166123135980521</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.271377169430279</v>
       </c>
       <c r="E55">
-        <v>-20.39883023743926</v>
+        <v>-15.38821865912026</v>
       </c>
       <c r="F55">
-        <v>0.195381073478992</v>
+        <v>1.12036262320181</v>
       </c>
       <c r="G55">
-        <v>-5.856388757145034</v>
+        <v>-0.6528537034349527</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.499724619956366</v>
       </c>
       <c r="E56">
-        <v>-20.25335300994285</v>
+        <v>-14.54498057109998</v>
       </c>
       <c r="F56">
-        <v>0.2792764672997204</v>
+        <v>1.16716206799037</v>
       </c>
       <c r="G56">
-        <v>-5.74135897293558</v>
+        <v>-0.09524947406603666</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.719565193968621</v>
       </c>
       <c r="E57">
-        <v>-20.15927849090751</v>
+        <v>-14.59078608568756</v>
       </c>
       <c r="F57">
-        <v>0.1357502176210668</v>
+        <v>0.8957872500984468</v>
       </c>
       <c r="G57">
-        <v>-5.70277508861807</v>
+        <v>-1.072554753103526</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.926892030974152</v>
       </c>
       <c r="E58">
-        <v>-19.25188551162056</v>
+        <v>-13.69543431878701</v>
       </c>
       <c r="F58">
-        <v>0.2600856796790642</v>
+        <v>0.8607555926340558</v>
       </c>
       <c r="G58">
-        <v>-5.49689812309227</v>
+        <v>-1.031536202388908</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.114823390430645</v>
       </c>
       <c r="E59">
-        <v>-19.22467843978248</v>
+        <v>-12.3875430982617</v>
       </c>
       <c r="F59">
-        <v>0.2514565764441018</v>
+        <v>1.502544835096612</v>
       </c>
       <c r="G59">
-        <v>-5.877437793448872</v>
+        <v>-1.534265282397671</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.280194525473665</v>
       </c>
       <c r="E60">
-        <v>-18.97485158572732</v>
+        <v>-14.72158200045111</v>
       </c>
       <c r="F60">
-        <v>-0.1618275179562108</v>
+        <v>0.7696037003648037</v>
       </c>
       <c r="G60">
-        <v>-5.197188064631031</v>
+        <v>-1.104484320098483</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.416773717198603</v>
       </c>
       <c r="E61">
-        <v>-18.77295410056934</v>
+        <v>-13.8269095046517</v>
       </c>
       <c r="F61">
-        <v>-0.08526234728285527</v>
+        <v>1.059472648891629</v>
       </c>
       <c r="G61">
-        <v>-5.828357281362697</v>
+        <v>-1.495215464618719</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.521188257988662</v>
       </c>
       <c r="E62">
-        <v>-19.5530607324487</v>
+        <v>-13.11610211051173</v>
       </c>
       <c r="F62">
-        <v>-0.08177740561927775</v>
+        <v>0.9007276332887431</v>
       </c>
       <c r="G62">
-        <v>-6.095747307463407</v>
+        <v>-1.658643266829982</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.590445544025534</v>
       </c>
       <c r="E63">
-        <v>-18.67671044248433</v>
+        <v>-13.33564253040359</v>
       </c>
       <c r="F63">
-        <v>-0.1911865154462309</v>
+        <v>0.5449405203167442</v>
       </c>
       <c r="G63">
-        <v>-6.295258703163883</v>
+        <v>-2.68441218830047</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.622406442811419</v>
       </c>
       <c r="E64">
-        <v>-18.54333782601042</v>
+        <v>-10.77923291206753</v>
       </c>
       <c r="F64">
-        <v>-0.3001897252458122</v>
+        <v>0.6845369950365169</v>
       </c>
       <c r="G64">
-        <v>-6.044953997723202</v>
+        <v>-1.348288925629904</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.617370719579494</v>
       </c>
       <c r="E65">
-        <v>-18.63554208528059</v>
+        <v>-12.52512266708873</v>
       </c>
       <c r="F65">
-        <v>-0.4315571981861746</v>
+        <v>1.022424745168824</v>
       </c>
       <c r="G65">
-        <v>-5.924690665126435</v>
+        <v>-2.551420997274616</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.576091022946547</v>
       </c>
       <c r="E66">
-        <v>-19.30003677574412</v>
+        <v>-13.11977923140596</v>
       </c>
       <c r="F66">
-        <v>-0.4276166544510573</v>
+        <v>0.8149203675023535</v>
       </c>
       <c r="G66">
-        <v>-6.131735745527396</v>
+        <v>-1.996257996745927</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.499518965586277</v>
       </c>
       <c r="E67">
-        <v>-17.82317913304461</v>
+        <v>-12.02767432582015</v>
       </c>
       <c r="F67">
-        <v>-0.5972182532350337</v>
+        <v>0.08794347807070176</v>
       </c>
       <c r="G67">
-        <v>-6.744336529454166</v>
+        <v>-2.374113627866902</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.390203730027144</v>
       </c>
       <c r="E68">
-        <v>-18.1194273741524</v>
+        <v>-12.16316173965564</v>
       </c>
       <c r="F68">
-        <v>-0.6223799130950687</v>
+        <v>0.6194140632980309</v>
       </c>
       <c r="G68">
-        <v>-7.061105658802958</v>
+        <v>-1.877743555240343</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.248345597499644</v>
       </c>
       <c r="E69">
-        <v>-17.57023668887217</v>
+        <v>-12.52409017501498</v>
       </c>
       <c r="F69">
-        <v>-0.77499252481503</v>
+        <v>0.7562984631410381</v>
       </c>
       <c r="G69">
-        <v>-6.637083240340596</v>
+        <v>-3.028786234628871</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.076881106304486</v>
       </c>
       <c r="E70">
-        <v>-18.00877864024898</v>
+        <v>-11.86005286042623</v>
       </c>
       <c r="F70">
-        <v>-0.6771051771936153</v>
+        <v>0.24495223559732</v>
       </c>
       <c r="G70">
-        <v>-6.402318400205445</v>
+        <v>-2.694567569026951</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.878396929434283</v>
       </c>
       <c r="E71">
-        <v>-18.197126931176</v>
+        <v>-12.44233763375451</v>
       </c>
       <c r="F71">
-        <v>-0.8592532286603929</v>
+        <v>0.1953595359265193</v>
       </c>
       <c r="G71">
-        <v>-6.897930510651772</v>
+        <v>-2.873778046939143</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.656400921442844</v>
       </c>
       <c r="E72">
-        <v>-18.47305590941138</v>
+        <v>-12.17096430037085</v>
       </c>
       <c r="F72">
-        <v>-0.9411961605127228</v>
+        <v>0.139447221339761</v>
       </c>
       <c r="G72">
-        <v>-6.596671715614475</v>
+        <v>-2.793397962397426</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.417611394302227</v>
       </c>
       <c r="E73">
-        <v>-17.78678378744496</v>
+        <v>-13.01278497602673</v>
       </c>
       <c r="F73">
-        <v>-1.045200173036409</v>
+        <v>0.0992622902625542</v>
       </c>
       <c r="G73">
-        <v>-6.45783338776969</v>
+        <v>-2.463602383457638</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.165452178996476</v>
       </c>
       <c r="E74">
-        <v>-18.26698317121833</v>
+        <v>-12.35337576187382</v>
       </c>
       <c r="F74">
-        <v>-1.017414245244305</v>
+        <v>0.1583497371042429</v>
       </c>
       <c r="G74">
-        <v>-6.291961075496642</v>
+        <v>-2.50891277197201</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.9086127404452334</v>
       </c>
       <c r="E75">
-        <v>-18.13096592592394</v>
+        <v>-13.2404177789703</v>
       </c>
       <c r="F75">
-        <v>-1.212480686357741</v>
+        <v>0.01564357115436091</v>
       </c>
       <c r="G75">
-        <v>-6.414084860717614</v>
+        <v>-2.137990362006142</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.6514500715269711</v>
       </c>
       <c r="E76">
-        <v>-18.32599371601228</v>
+        <v>-12.61403925422934</v>
       </c>
       <c r="F76">
-        <v>-1.176592496998855</v>
+        <v>-0.6327071695057701</v>
       </c>
       <c r="G76">
-        <v>-5.937454616992675</v>
+        <v>-2.795084510278981</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.400985825912435</v>
       </c>
       <c r="E77">
-        <v>-18.33722886002531</v>
+        <v>-13.57604110157478</v>
       </c>
       <c r="F77">
-        <v>-1.20762148317292</v>
+        <v>-0.4302500344245569</v>
       </c>
       <c r="G77">
-        <v>-5.629899157782803</v>
+        <v>-1.505954902782782</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.1630269121128817</v>
       </c>
       <c r="E78">
-        <v>-19.14811100126079</v>
+        <v>-13.64127829812928</v>
       </c>
       <c r="F78">
-        <v>-1.270671011302198</v>
+        <v>-0.6199503115026578</v>
       </c>
       <c r="G78">
-        <v>-5.960147545297795</v>
+        <v>-2.986908003865679</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.05828922756298173</v>
       </c>
       <c r="E79">
-        <v>-19.94380464067454</v>
+        <v>-14.92063107545826</v>
       </c>
       <c r="F79">
-        <v>-1.377044154597891</v>
+        <v>-0.5712033749501152</v>
       </c>
       <c r="G79">
-        <v>-5.538421981927043</v>
+        <v>-2.17953718939183</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.2563038955122512</v>
       </c>
       <c r="E80">
-        <v>-20.04514736049219</v>
+        <v>-14.59660970326143</v>
       </c>
       <c r="F80">
-        <v>-1.437497579286796</v>
+        <v>-0.685468374492279</v>
       </c>
       <c r="G80">
-        <v>-4.759709356553386</v>
+        <v>-2.428955965011461</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.4284882711908682</v>
       </c>
       <c r="E81">
-        <v>-20.72700874877513</v>
+        <v>-14.66388924159338</v>
       </c>
       <c r="F81">
-        <v>-1.539673384952504</v>
+        <v>-0.5160639271501689</v>
       </c>
       <c r="G81">
-        <v>-5.026899228138969</v>
+        <v>-1.723375205754707</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.5688953813702236</v>
       </c>
       <c r="E82">
-        <v>-21.43381297189232</v>
+        <v>-15.93958301192416</v>
       </c>
       <c r="F82">
-        <v>-1.440819332572022</v>
+        <v>-1.03049416653451</v>
       </c>
       <c r="G82">
-        <v>-5.12308823815409</v>
+        <v>-1.025551254264481</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.6756569442238065</v>
       </c>
       <c r="E83">
-        <v>-21.41544548131721</v>
+        <v>-16.64401884313534</v>
       </c>
       <c r="F83">
-        <v>-1.584480606137332</v>
+        <v>-0.3840470141660117</v>
       </c>
       <c r="G83">
-        <v>-4.874233832642685</v>
+        <v>-1.522338042029089</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.7469357593179825</v>
       </c>
       <c r="E84">
-        <v>-22.86609231646033</v>
+        <v>-18.79137140435854</v>
       </c>
       <c r="F84">
-        <v>-1.569551768804079</v>
+        <v>-0.3629385560078747</v>
       </c>
       <c r="G84">
-        <v>-5.016304163723522</v>
+        <v>-1.132834074372085</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.7827516198440477</v>
       </c>
       <c r="E85">
-        <v>-24.24757576808429</v>
+        <v>-19.62980025298268</v>
       </c>
       <c r="F85">
-        <v>-1.434509658064898</v>
+        <v>-0.1611225772964284</v>
       </c>
       <c r="G85">
-        <v>-5.325421484395689</v>
+        <v>-1.321668375118129</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.7846465225805022</v>
       </c>
       <c r="E86">
-        <v>-24.43614142576369</v>
+        <v>-20.27422474664421</v>
       </c>
       <c r="F86">
-        <v>-1.750985767569644</v>
+        <v>-0.8617722939323063</v>
       </c>
       <c r="G86">
-        <v>-5.231942763388669</v>
+        <v>-1.087631966169175</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.7547036237192235</v>
       </c>
       <c r="E87">
-        <v>-25.58637835218596</v>
+        <v>-21.29247929811293</v>
       </c>
       <c r="F87">
-        <v>-1.856116359761138</v>
+        <v>-0.29521206552239</v>
       </c>
       <c r="G87">
-        <v>-4.509650742729663</v>
+        <v>-1.547124389689134</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.6966564808602027</v>
       </c>
       <c r="E88">
-        <v>-26.25536076039109</v>
+        <v>-23.6113795116947</v>
       </c>
       <c r="F88">
-        <v>-1.73455924197213</v>
+        <v>-0.7387307417574817</v>
       </c>
       <c r="G88">
-        <v>-4.711183370910757</v>
+        <v>-0.465853605540639</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.6146762814955188</v>
       </c>
       <c r="E89">
-        <v>-28.18180983104612</v>
+        <v>-24.98121572817094</v>
       </c>
       <c r="F89">
-        <v>-1.541539696711011</v>
+        <v>-0.4446230372305312</v>
       </c>
       <c r="G89">
-        <v>-5.31974497109785</v>
+        <v>-1.046101544891283</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.5137011992818749</v>
       </c>
       <c r="E90">
-        <v>-29.0863272293382</v>
+        <v>-26.97380316170799</v>
       </c>
       <c r="F90">
-        <v>-1.814326881024708</v>
+        <v>-1.362560978927345</v>
       </c>
       <c r="G90">
-        <v>-5.176621367896431</v>
+        <v>-0.5644543134019526</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.3991470834691386</v>
       </c>
       <c r="E91">
-        <v>-31.01270837288312</v>
+        <v>-26.43039986620957</v>
       </c>
       <c r="F91">
-        <v>-1.661172517023316</v>
+        <v>-0.8191138577903401</v>
       </c>
       <c r="G91">
-        <v>-5.259137527673347</v>
+        <v>-2.335053966423272</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.2766701532054873</v>
       </c>
       <c r="E92">
-        <v>-32.34443748058481</v>
+        <v>-28.98655589000121</v>
       </c>
       <c r="F92">
-        <v>-1.575724762689741</v>
+        <v>-0.9071577155642884</v>
       </c>
       <c r="G92">
-        <v>-5.277345026106706</v>
+        <v>-1.717898846971994</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.1508194922237012</v>
       </c>
       <c r="E93">
-        <v>-33.87475375894487</v>
+        <v>-30.73757414183609</v>
       </c>
       <c r="F93">
-        <v>-1.796188120005607</v>
+        <v>-1.101213548446309</v>
       </c>
       <c r="G93">
-        <v>-5.899566351645767</v>
+        <v>-1.981892808758678</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.02737183553142365</v>
       </c>
       <c r="E94">
-        <v>-36.04179838939042</v>
+        <v>-32.6269327461313</v>
       </c>
       <c r="F94">
-        <v>-1.839453749453825</v>
+        <v>-1.264831849479864</v>
       </c>
       <c r="G94">
-        <v>-5.975493818531318</v>
+        <v>-2.813544662772417</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.09005729479437737</v>
       </c>
       <c r="E95">
-        <v>-37.70674619999852</v>
+        <v>-35.85086207556801</v>
       </c>
       <c r="F95">
-        <v>-1.732280403247028</v>
+        <v>-1.348750437587871</v>
       </c>
       <c r="G95">
-        <v>-5.516897168497086</v>
+        <v>-2.419827606633086</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.1970562999378376</v>
       </c>
       <c r="E96">
-        <v>-39.46826145458319</v>
+        <v>-38.23965475698417</v>
       </c>
       <c r="F96">
-        <v>-1.656932104288385</v>
+        <v>-1.307748736251504</v>
       </c>
       <c r="G96">
-        <v>-7.085311230246981</v>
+        <v>-3.109655221182946</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.2902989960598132</v>
       </c>
       <c r="E97">
-        <v>-42.36755580359502</v>
+        <v>-38.64205722154276</v>
       </c>
       <c r="F97">
-        <v>-1.850491745096129</v>
+        <v>-0.9811491487171458</v>
       </c>
       <c r="G97">
-        <v>-6.807526294245951</v>
+        <v>-3.133578607572857</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.3686923200357592</v>
       </c>
       <c r="E98">
-        <v>-43.86947628568999</v>
+        <v>-41.39748195133091</v>
       </c>
       <c r="F98">
-        <v>-1.768174391177734</v>
+        <v>-0.8553002594142337</v>
       </c>
       <c r="G98">
-        <v>-7.787371238770452</v>
+        <v>-2.865154996680923</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.4296587075656755</v>
       </c>
       <c r="E99">
-        <v>-45.35921064423031</v>
+        <v>-43.26725264130594</v>
       </c>
       <c r="F99">
-        <v>-2.212055063967849</v>
+        <v>-1.2320864860472</v>
       </c>
       <c r="G99">
-        <v>-7.547678003853015</v>
+        <v>-4.37293208401228</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.4771912373084854</v>
       </c>
       <c r="E100">
-        <v>-47.70178345568718</v>
+        <v>-46.1940099209373</v>
       </c>
       <c r="F100">
-        <v>-1.994264019893414</v>
+        <v>-1.339701352079689</v>
       </c>
       <c r="G100">
-        <v>-8.302060371363391</v>
+        <v>-4.610410494377092</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.5084084298774778</v>
       </c>
       <c r="E101">
-        <v>-49.57943595467255</v>
+        <v>-47.63331745716521</v>
       </c>
       <c r="F101">
-        <v>-2.073339972164655</v>
+        <v>-1.875661688630192</v>
       </c>
       <c r="G101">
-        <v>-8.344821250726074</v>
+        <v>-4.640181017585934</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.5333030902512357</v>
       </c>
       <c r="E102">
-        <v>-51.53849343453832</v>
+        <v>-50.25506842695795</v>
       </c>
       <c r="F102">
-        <v>-2.231524183035845</v>
+        <v>-2.327889819738318</v>
       </c>
       <c r="G102">
-        <v>-8.705253595366397</v>
+        <v>-5.367342371039156</v>
       </c>
     </row>
   </sheetData>
